--- a/course_enrollment_forms/016_course_overview_acknowledgement_form--course_enrollment_forms.xlsx
+++ b/course_enrollment_forms/016_course_overview_acknowledgement_form--course_enrollment_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>course_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Course Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>course_details</t>
+          <t>student_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>course_details</t>
+          <t>Student Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,18 +556,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>acknowledgement</t>
+          <t>parent_details</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>acknowledgement</t>
+          <t>Parent Information</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,18 +579,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>course_director</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>Course Director</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,18 +602,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>parent_consent</t>
+          <t>student_address</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>parent_consent</t>
+          <t>Student's Address</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,18 +625,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>student_consent</t>
+          <t>parent_address</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>student_consent</t>
+          <t>Parent's Address</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>acknowledgement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>Acknowledgement</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>parent_name</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>parent_name</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Submission Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Submission Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,18 +740,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>acknowledgement_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Acknowledgement Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -763,499 +763,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>acknowledgement_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>Acknowledgement Time</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>submitted_date</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>submitted_date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>acknowledgement_date</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>acknowledgement_date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>acknowledgement_time</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>acknowledgement_time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>parent_signature</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>parent_signature</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>student_signature</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>student_signature</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>acknowledgement_text</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>acknowledgement_text</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submitted_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>submitted_date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>acknowledgement_date</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>acknowledgement_date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>acknowledgement_time</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>acknowledgement_time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>parent_signature</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>parent_signature</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>student_signature</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>student_signature</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>acknowledgement_text</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>acknowledgement_text</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>submitted_date</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>submitted_date</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>acknowledgement_date</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>acknowledgement_date</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>acknowledgement_time</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>acknowledgement_time</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
